--- a/naver-place-crawler/results_hair/안양_미용실.xlsx
+++ b/naver-place-crawler/results_hair/안양_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V478"/>
+  <dimension ref="A1:V526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -42367,45 +42367,49 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>생활,편의</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>키키헤어</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr"/>
+          <t>나이스가이 평촌트리지아점</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>jungwoo4094600@naver.com</t>
+        </is>
+      </c>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0507-1322-5493</t>
+          <t>031-689-5856</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관악대로 103 3층, 키키헤어 미용실</t>
+          <t>경기도 안양시 동안구 호계동 928-7 평촌트리지아1단지 상가 1015호</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.iniceguy.com/</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -42421,17 +42425,17 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P452" t="n">
-        <v>1047</v>
+        <v>64</v>
       </c>
       <c r="Q452" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="R452" t="n">
-        <v>1109</v>
+        <v>91</v>
       </c>
       <c r="S452" t="inlineStr">
         <is>
@@ -42440,12 +42444,12 @@
       </c>
       <c r="T452" t="inlineStr">
         <is>
-          <t>1162671504</t>
+          <t>1409764741</t>
         </is>
       </c>
       <c r="U452" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1162671504</t>
+          <t>https://m.place.naver.com/place/1409764741</t>
         </is>
       </c>
       <c r="V452" t="inlineStr">
@@ -42457,34 +42461,34 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>보스타바버샵</t>
+          <t>리안헤어 안양일번가2호점</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>gusdkalsu@naver.com</t>
+          <t>whtnqls0705@naver.com</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0507-1310-9655</t>
+          <t>0507-1410-0959</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 동편로39번길 20-13 1층</t>
+          <t>경기도 안양시 만안구 안양로304번길 35 2층, 3층 리안헤어 안양일번가2호점</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>http://instagram.com/bosstha_barbershop</t>
+          <t>https://www.instagram.com/riahnhair._.anyang._.2</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -42519,13 +42523,13 @@
         </is>
       </c>
       <c r="P453" t="n">
-        <v>1184</v>
+        <v>6712</v>
       </c>
       <c r="Q453" t="n">
-        <v>17</v>
+        <v>2400</v>
       </c>
       <c r="R453" t="n">
-        <v>1201</v>
+        <v>9112</v>
       </c>
       <c r="S453" t="inlineStr">
         <is>
@@ -42534,12 +42538,12 @@
       </c>
       <c r="T453" t="inlineStr">
         <is>
-          <t>1585300866</t>
+          <t>38420166</t>
         </is>
       </c>
       <c r="U453" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585300866</t>
+          <t>https://m.place.naver.com/place/38420166</t>
         </is>
       </c>
       <c r="V453" t="inlineStr">
@@ -42551,29 +42555,25 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>영진이발관</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>kyakult@naver.com</t>
-        </is>
-      </c>
+          <t>수호헤어</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>031-471-6317</t>
+          <t>031-360-0176</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 석천로171번길 5</t>
+          <t>경기도 안양시 만안구 양화로147번길 7 1층 103호 Soohohair 수호헤어</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -42613,13 +42613,13 @@
         </is>
       </c>
       <c r="P454" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="Q454" t="n">
         <v>0</v>
       </c>
       <c r="R454" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="S454" t="inlineStr">
         <is>
@@ -42628,12 +42628,12 @@
       </c>
       <c r="T454" t="inlineStr">
         <is>
-          <t>1107419428</t>
+          <t>1450168662</t>
         </is>
       </c>
       <c r="U454" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107419428</t>
+          <t>https://m.place.naver.com/place/1450168662</t>
         </is>
       </c>
       <c r="V454" t="inlineStr">
@@ -42645,34 +42645,34 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>하우디바버샵 안양점</t>
+          <t>지니헤어</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>tlsehd2036@naver.com</t>
+          <t>parkjunmasan@naver.com</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0507-1440-2807</t>
+          <t>031-421-6611</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로323번길 10 1층 하우디바버샵 안양점</t>
+          <t>경기도 안양시 동안구 흥안대로 426-6</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tlsehd2036</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -42682,12 +42682,12 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -42703,17 +42703,17 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P455" t="n">
-        <v>910</v>
+        <v>72</v>
       </c>
       <c r="Q455" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R455" t="n">
-        <v>966</v>
+        <v>72</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -42722,12 +42722,12 @@
       </c>
       <c r="T455" t="inlineStr">
         <is>
-          <t>1190201605</t>
+          <t>1933035602</t>
         </is>
       </c>
       <c r="U455" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1190201605</t>
+          <t>https://m.place.naver.com/place/1933035602</t>
         </is>
       </c>
       <c r="V455" t="inlineStr">
@@ -42739,21 +42739,25 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>정현이용원</t>
+          <t>장규철헤어</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr"/>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>031-423-5526</t>
+        </is>
+      </c>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 충훈로93번길 26</t>
+          <t>경기도 안양시 동안구 평의길 33 2층</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -42793,13 +42797,13 @@
         </is>
       </c>
       <c r="P456" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Q456" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R456" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S456" t="inlineStr">
         <is>
@@ -42808,12 +42812,12 @@
       </c>
       <c r="T456" t="inlineStr">
         <is>
-          <t>1850328269</t>
+          <t>34490762</t>
         </is>
       </c>
       <c r="U456" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850328269</t>
+          <t>https://m.place.naver.com/place/34490762</t>
         </is>
       </c>
       <c r="V456" t="inlineStr">
@@ -42825,34 +42829,34 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>루앤헤어 안양호계점</t>
+          <t>리안헤어 범계점</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>ttlsunhwa@naver.com</t>
+          <t>riahn8300@naver.com</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0507-1317-3022</t>
+          <t>0507-1415-0670</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 포도원로 4 2층 루앤헤어 안양호계점</t>
+          <t>경기도 안양시 동안구 평촌대로 217 한솔센트럴파크1차 206호</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ttlsunhwa</t>
+          <t>https://www.instagram.com/riahnb4</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -42867,7 +42871,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -42883,17 +42887,17 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P457" t="n">
-        <v>2449</v>
+        <v>7683</v>
       </c>
       <c r="Q457" t="n">
-        <v>249</v>
+        <v>393</v>
       </c>
       <c r="R457" t="n">
-        <v>2698</v>
+        <v>8076</v>
       </c>
       <c r="S457" t="inlineStr">
         <is>
@@ -42902,12 +42906,12 @@
       </c>
       <c r="T457" t="inlineStr">
         <is>
-          <t>1012904876</t>
+          <t>12751649</t>
         </is>
       </c>
       <c r="U457" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012904876</t>
+          <t>https://m.place.naver.com/place/12751649</t>
         </is>
       </c>
       <c r="V457" t="inlineStr">
@@ -42919,34 +42923,34 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>선이발관</t>
+          <t>어라운디헤어</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>soyen5046@naver.com</t>
+          <t>aroun_d_hair@naver.com</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>031-472-5606</t>
+          <t>0507-1467-7867</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 석수로16번길 56</t>
+          <t>경기도 안양시 동안구 시민대로 280 2층</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/aroun_d_hair</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -42956,12 +42960,12 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -42977,17 +42981,17 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P458" t="n">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="Q458" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="R458" t="n">
-        <v>1</v>
+        <v>2235</v>
       </c>
       <c r="S458" t="inlineStr">
         <is>
@@ -42996,12 +43000,12 @@
       </c>
       <c r="T458" t="inlineStr">
         <is>
-          <t>37146070</t>
+          <t>1470434324</t>
         </is>
       </c>
       <c r="U458" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37146070</t>
+          <t>https://m.place.naver.com/place/1470434324</t>
         </is>
       </c>
       <c r="V458" t="inlineStr">
@@ -43013,30 +43017,34 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>현대이발관</t>
+          <t>미봉헤어 본점</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>sacheoncity@naver.com</t>
+          <t>mrbong_hair@naver.com</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
-      <c r="E459" t="inlineStr"/>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>0507-1490-7404</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 귀인로 195</t>
+          <t>경기도 안양시 동안구 평촌대로223번길 11 성우프라자 404호</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mrbong_hair</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -43046,12 +43054,12 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -43067,17 +43075,17 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P459" t="n">
-        <v>0</v>
+        <v>1812</v>
       </c>
       <c r="Q459" t="n">
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="R459" t="n">
-        <v>0</v>
+        <v>2261</v>
       </c>
       <c r="S459" t="inlineStr">
         <is>
@@ -43086,12 +43094,12 @@
       </c>
       <c r="T459" t="inlineStr">
         <is>
-          <t>21136803</t>
+          <t>1358426843</t>
         </is>
       </c>
       <c r="U459" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21136803</t>
+          <t>https://m.place.naver.com/place/1358426843</t>
         </is>
       </c>
       <c r="V459" t="inlineStr">
@@ -43103,25 +43111,25 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>현대이발관</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>sacheoncity@naver.com</t>
-        </is>
-      </c>
+          <t>라블랑코 범계역점</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
-      <c r="E460" t="inlineStr"/>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>031-383-0804</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 양화로 156</t>
+          <t>경기도 안양시 동안구 평촌대로223번길 55 2층 201~203호</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -43161,13 +43169,13 @@
         </is>
       </c>
       <c r="P460" t="n">
-        <v>0</v>
+        <v>3825</v>
       </c>
       <c r="Q460" t="n">
-        <v>0</v>
+        <v>1721</v>
       </c>
       <c r="R460" t="n">
-        <v>0</v>
+        <v>5546</v>
       </c>
       <c r="S460" t="inlineStr">
         <is>
@@ -43176,12 +43184,12 @@
       </c>
       <c r="T460" t="inlineStr">
         <is>
-          <t>2093976829</t>
+          <t>1608783820</t>
         </is>
       </c>
       <c r="U460" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093976829</t>
+          <t>https://m.place.naver.com/place/1608783820</t>
         </is>
       </c>
       <c r="V460" t="inlineStr">
@@ -43193,34 +43201,34 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>동보이발관</t>
+          <t>헤어은</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>chogoya008@naver.com</t>
+          <t>haireun3832429@naver.com</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
-          <t>031-471-6971</t>
+          <t>0507-1416-2429</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 경수대로1201번길 30</t>
+          <t>경기도 안양시 동안구 평촌대로 141 트윈프라자 202호</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/haireun3832429</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -43230,12 +43238,12 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -43251,17 +43259,17 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P461" t="n">
-        <v>1</v>
+        <v>487</v>
       </c>
       <c r="Q461" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R461" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -43270,12 +43278,12 @@
       </c>
       <c r="T461" t="inlineStr">
         <is>
-          <t>37146881</t>
+          <t>1944670718</t>
         </is>
       </c>
       <c r="U461" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37146881</t>
+          <t>https://m.place.naver.com/place/1944670718</t>
         </is>
       </c>
       <c r="V461" t="inlineStr">
@@ -43287,34 +43295,34 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>로지바버샵</t>
+          <t>레아헤어</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>k_s89@naver.com</t>
+          <t>gpfus0078@naver.com</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
-          <t>0507-1362-3431</t>
+          <t>031-471-5128</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 시민대로159번길 25 134호 로지바버샵</t>
+          <t>경기도 안양시 만안구 와룡로 18-1</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/k_s89</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -43324,12 +43332,12 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -43345,17 +43353,17 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P462" t="n">
-        <v>922</v>
+        <v>86</v>
       </c>
       <c r="Q462" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R462" t="n">
-        <v>1056</v>
+        <v>86</v>
       </c>
       <c r="S462" t="inlineStr">
         <is>
@@ -43364,12 +43372,12 @@
       </c>
       <c r="T462" t="inlineStr">
         <is>
-          <t>1046981391</t>
+          <t>37146269</t>
         </is>
       </c>
       <c r="U462" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046981391</t>
+          <t>https://m.place.naver.com/place/37146269</t>
         </is>
       </c>
       <c r="V462" t="inlineStr">
@@ -43381,34 +43389,30 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>행운이발관</t>
+          <t>김세린헤어</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>knta_pr@naver.com</t>
+          <t>kimserinhair@naver.com</t>
         </is>
       </c>
       <c r="D463" t="inlineStr"/>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>031-441-5607</t>
-        </is>
-      </c>
+      <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로532번길 41</t>
+          <t>경기도 안양시 동안구 관평로 122 초원아파트 상가동204호</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/kimserinhair</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -43418,12 +43422,12 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -43443,13 +43447,13 @@
         </is>
       </c>
       <c r="P463" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q463" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R463" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S463" t="inlineStr">
         <is>
@@ -43458,12 +43462,12 @@
       </c>
       <c r="T463" t="inlineStr">
         <is>
-          <t>21137869</t>
+          <t>36397886</t>
         </is>
       </c>
       <c r="U463" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21137869</t>
+          <t>https://m.place.naver.com/place/36397886</t>
         </is>
       </c>
       <c r="V463" t="inlineStr">
@@ -43475,43 +43479,39 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>리벨로 바버샵</t>
+          <t>마이헤어가든 안양호계점</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>rebello1015@naver.com</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>ceo@rebello.co.kr</t>
-        </is>
-      </c>
+          <t>myhairgarden@naver.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
-          <t>0507-1437-5892</t>
+          <t>0507-1336-4581</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 시민대로 408 스페이스 블레스 유 2층 리벨로 바버샵</t>
+          <t>경기도 안양시 동안구 경수대로 556 3층</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>https://www.bellobellagroup.com/</t>
+          <t>https://www.instagram.com/_myhairgarden</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -43521,18 +43521,22 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M464" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -43541,13 +43545,13 @@
         </is>
       </c>
       <c r="P464" t="n">
-        <v>1597</v>
+        <v>332</v>
       </c>
       <c r="Q464" t="n">
-        <v>409</v>
+        <v>121</v>
       </c>
       <c r="R464" t="n">
-        <v>2006</v>
+        <v>453</v>
       </c>
       <c r="S464" t="inlineStr">
         <is>
@@ -43556,12 +43560,12 @@
       </c>
       <c r="T464" t="inlineStr">
         <is>
-          <t>83867576</t>
+          <t>1700428934</t>
         </is>
       </c>
       <c r="U464" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/83867576</t>
+          <t>https://m.place.naver.com/place/1700428934</t>
         </is>
       </c>
       <c r="V464" t="inlineStr">
@@ -43573,30 +43577,34 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>슬리커바버샵</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr"/>
+          <t>임스헤어</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>gonavy207@naver.com</t>
+        </is>
+      </c>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
-          <t>0507-1328-1979</t>
+          <t>031-388-7627</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 장내로139번길 56-4 2층 슬리커바버샵</t>
+          <t>경기도 안양시 동안구 관악대로106번길 77 비산롯데캐슬 상가동</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>http://www.instargram.com/barber__yoonhyuk</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -43606,7 +43614,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -43631,13 +43639,13 @@
         </is>
       </c>
       <c r="P465" t="n">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="Q465" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R465" t="n">
-        <v>489</v>
+        <v>83</v>
       </c>
       <c r="S465" t="inlineStr">
         <is>
@@ -43646,12 +43654,12 @@
       </c>
       <c r="T465" t="inlineStr">
         <is>
-          <t>1339445993</t>
+          <t>21161884</t>
         </is>
       </c>
       <c r="U465" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1339445993</t>
+          <t>https://m.place.naver.com/place/21161884</t>
         </is>
       </c>
       <c r="V465" t="inlineStr">
@@ -43663,25 +43671,21 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>뉴금강이발관</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>orseti8300@naver.com</t>
-        </is>
-      </c>
+          <t>공간헤어</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 양화로135번길 25</t>
+          <t>경기도 안양시 만안구 석수로6번길 44</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -43721,10 +43725,10 @@
         </is>
       </c>
       <c r="P466" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q466" t="n">
         <v>0</v>
-      </c>
-      <c r="Q466" t="n">
-        <v>1</v>
       </c>
       <c r="R466" t="n">
         <v>1</v>
@@ -43736,12 +43740,12 @@
       </c>
       <c r="T466" t="inlineStr">
         <is>
-          <t>37145080</t>
+          <t>1365391531</t>
         </is>
       </c>
       <c r="U466" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37145080</t>
+          <t>https://m.place.naver.com/place/1365391531</t>
         </is>
       </c>
       <c r="V466" t="inlineStr">
@@ -43753,34 +43757,30 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>레고코르누바버샵 안양</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>sunung418@naver.com</t>
-        </is>
-      </c>
+          <t>머리못하는집 충훈74호점</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
-          <t>0507-1486-0400</t>
+          <t>031-473-9146</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로323번길 40 2층 레고코르누 바버샵</t>
+          <t>경기도 안양시 만안구 충훈로83번길 10</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/regocornubarbershop/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -43790,7 +43790,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
@@ -43811,17 +43811,17 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P467" t="n">
-        <v>844</v>
+        <v>190</v>
       </c>
       <c r="Q467" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="R467" t="n">
-        <v>867</v>
+        <v>191</v>
       </c>
       <c r="S467" t="inlineStr">
         <is>
@@ -43830,12 +43830,12 @@
       </c>
       <c r="T467" t="inlineStr">
         <is>
-          <t>1824492157</t>
+          <t>37147757</t>
         </is>
       </c>
       <c r="U467" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824492157</t>
+          <t>https://m.place.naver.com/place/37147757</t>
         </is>
       </c>
       <c r="V467" t="inlineStr">
@@ -43847,30 +43847,34 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>남자는머리빨</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr"/>
+          <t>이가자헤어비스 평촌이마트점</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>esthe34@naver.com</t>
+        </is>
+      </c>
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
-          <t>0507-1354-0380</t>
+          <t>0507-1455-0476</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 박달로 501 1층 103호</t>
+          <t>경기도 안양시 동안구 시민대로 300 이마트 평촌점 지하1층 이가자헤어비스</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/leekaja__pc</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -43880,7 +43884,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -43901,17 +43905,17 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P468" t="n">
-        <v>7</v>
+        <v>2356</v>
       </c>
       <c r="Q468" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R468" t="n">
-        <v>8</v>
+        <v>2366</v>
       </c>
       <c r="S468" t="inlineStr">
         <is>
@@ -43920,12 +43924,12 @@
       </c>
       <c r="T468" t="inlineStr">
         <is>
-          <t>1667477062</t>
+          <t>12866016</t>
         </is>
       </c>
       <c r="U468" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1667477062</t>
+          <t>https://m.place.naver.com/place/12866016</t>
         </is>
       </c>
       <c r="V468" t="inlineStr">
@@ -43937,25 +43941,29 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>석수이발관</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr"/>
+          <t>에스제이헤어</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>emkim1003@naver.com</t>
+        </is>
+      </c>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
-          <t>031-471-8137</t>
+          <t>031-422-8891</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 경수대로1200번길 5</t>
+          <t>경기도 안양시 동안구 흥안대로434번길 19-33 102호</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -43995,13 +44003,13 @@
         </is>
       </c>
       <c r="P469" t="n">
-        <v>1</v>
+        <v>363</v>
       </c>
       <c r="Q469" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R469" t="n">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="S469" t="inlineStr">
         <is>
@@ -44010,12 +44018,12 @@
       </c>
       <c r="T469" t="inlineStr">
         <is>
-          <t>18636113</t>
+          <t>1117076919</t>
         </is>
       </c>
       <c r="U469" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18636113</t>
+          <t>https://m.place.naver.com/place/1117076919</t>
         </is>
       </c>
       <c r="V469" t="inlineStr">
@@ -44027,30 +44035,30 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>청주이발소</t>
+          <t>하라주쿠헤어 안양점</t>
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
-          <t>031-383-6995</t>
+          <t>0507-1378-1263</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관평로138번길 53 초원부영아파트 상가동 2층</t>
+          <t>경기도 안양시 만안구 만안로 219 2층 하라주쿠헤어 안양점</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/harajuku_hair/</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -44060,7 +44068,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
@@ -44081,17 +44089,17 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P470" t="n">
-        <v>5</v>
+        <v>3737</v>
       </c>
       <c r="Q470" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="R470" t="n">
-        <v>5</v>
+        <v>3967</v>
       </c>
       <c r="S470" t="inlineStr">
         <is>
@@ -44100,12 +44108,12 @@
       </c>
       <c r="T470" t="inlineStr">
         <is>
-          <t>1203918736</t>
+          <t>1074696423</t>
         </is>
       </c>
       <c r="U470" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1203918736</t>
+          <t>https://m.place.naver.com/place/1074696423</t>
         </is>
       </c>
       <c r="V470" t="inlineStr">
@@ -44117,25 +44125,25 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>초원이발관</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>gunsanpr@naver.com</t>
-        </is>
-      </c>
+          <t>봄헤어샵</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr"/>
-      <c r="E471" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>031-422-0030</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 양화로105번길 63</t>
+          <t>경기도 안양시 동안구 부림로 48</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -44175,13 +44183,13 @@
         </is>
       </c>
       <c r="P471" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q471" t="n">
         <v>0</v>
       </c>
       <c r="R471" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -44190,12 +44198,12 @@
       </c>
       <c r="T471" t="inlineStr">
         <is>
-          <t>21148112</t>
+          <t>1459697947</t>
         </is>
       </c>
       <c r="U471" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21148112</t>
+          <t>https://m.place.naver.com/place/1459697947</t>
         </is>
       </c>
       <c r="V471" t="inlineStr">
@@ -44207,30 +44215,34 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>리웨이바버샵</t>
+          <t>자누스헤어</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>done_barber@naver.com</t>
+          <t>janus-hair@naver.com</t>
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr"/>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>0507-1370-6978</t>
+        </is>
+      </c>
       <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 귀인로190번길 70-31 1층</t>
+          <t>경기도 안양시 동안구 흥안대로456번길 56 뚜레쥬르 2층 자누스헤어</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/done_barber</t>
+          <t>https://www.instagram.com/kimdaekyoung_/</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -44245,7 +44257,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -44265,13 +44277,13 @@
         </is>
       </c>
       <c r="P472" t="n">
-        <v>223</v>
+        <v>385</v>
       </c>
       <c r="Q472" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="R472" t="n">
-        <v>231</v>
+        <v>518</v>
       </c>
       <c r="S472" t="inlineStr">
         <is>
@@ -44280,12 +44292,12 @@
       </c>
       <c r="T472" t="inlineStr">
         <is>
-          <t>1739150372</t>
+          <t>1510549642</t>
         </is>
       </c>
       <c r="U472" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739150372</t>
+          <t>https://m.place.naver.com/place/1510549642</t>
         </is>
       </c>
       <c r="V472" t="inlineStr">
@@ -44297,30 +44309,34 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>펜스바버샵 안양본점</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr"/>
+          <t>안양역붙임머리 센스</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>llsyll94230@naver.com</t>
+        </is>
+      </c>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0507-1345-1423</t>
+          <t>0507-1390-5828</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 시민대로 230 평촌아크로타워 221호</t>
+          <t>경기도 안양시 만안구 안양로 316 지하2층 218호</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fhns_barbershop/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -44330,7 +44346,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -44351,17 +44367,17 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P473" t="n">
-        <v>279</v>
+        <v>7</v>
       </c>
       <c r="Q473" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="R473" t="n">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="S473" t="inlineStr">
         <is>
@@ -44370,12 +44386,12 @@
       </c>
       <c r="T473" t="inlineStr">
         <is>
-          <t>1891047961</t>
+          <t>1773487384</t>
         </is>
       </c>
       <c r="U473" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1891047961</t>
+          <t>https://m.place.naver.com/place/1773487384</t>
         </is>
       </c>
       <c r="V473" t="inlineStr">
@@ -44387,30 +44403,34 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>밀리토바버샵</t>
+          <t>플러스82헤어 평촌점</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>style2232@naver.com</t>
+          <t>plusxx82@naver.com</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
-      <c r="E474" t="inlineStr"/>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>0507-1420-6333</t>
+        </is>
+      </c>
       <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 박달로479번길 23 1층</t>
+          <t>경기도 안양시 동안구 관평로182번길 20 2층</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/milito_barbershop/</t>
+          <t>https://blog.naver.com/plusxx82</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -44425,7 +44445,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -44445,13 +44465,13 @@
         </is>
       </c>
       <c r="P474" t="n">
-        <v>225</v>
+        <v>4035</v>
       </c>
       <c r="Q474" t="n">
-        <v>4</v>
+        <v>381</v>
       </c>
       <c r="R474" t="n">
-        <v>229</v>
+        <v>4416</v>
       </c>
       <c r="S474" t="inlineStr">
         <is>
@@ -44460,12 +44480,12 @@
       </c>
       <c r="T474" t="inlineStr">
         <is>
-          <t>1353887934</t>
+          <t>11736220</t>
         </is>
       </c>
       <c r="U474" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1353887934</t>
+          <t>https://m.place.naver.com/place/11736220</t>
         </is>
       </c>
       <c r="V474" t="inlineStr">
@@ -44477,25 +44497,25 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>준형이발관</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>hayeoneedy0u@naver.com</t>
-        </is>
-      </c>
+          <t>별헤어센스</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
-      <c r="E475" t="inlineStr"/>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>031-471-3228</t>
+        </is>
+      </c>
       <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 박달로479번길 10</t>
+          <t>경기도 안양시 만안구 석천로211번길 70</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -44535,13 +44555,13 @@
         </is>
       </c>
       <c r="P475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q475" t="n">
         <v>0</v>
       </c>
       <c r="R475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -44550,12 +44570,12 @@
       </c>
       <c r="T475" t="inlineStr">
         <is>
-          <t>37146400</t>
+          <t>19429351</t>
         </is>
       </c>
       <c r="U475" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37146400</t>
+          <t>https://m.place.naver.com/place/19429351</t>
         </is>
       </c>
       <c r="V475" t="inlineStr">
@@ -44567,34 +44587,30 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>상상나래헤어샵</t>
+          <t>수진헤어아트</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>sangx2narae1@naver.com</t>
+          <t>jimmini_@naver.com</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>031-383-1123</t>
-        </is>
-      </c>
+      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관악대로 317 2층</t>
+          <t>경기도 안양시 만안구 석수로16번길 32-18</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sangx2narae1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -44604,12 +44620,12 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -44625,17 +44641,17 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P476" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q476" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R476" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="S476" t="inlineStr">
         <is>
@@ -44644,12 +44660,12 @@
       </c>
       <c r="T476" t="inlineStr">
         <is>
-          <t>2085320924</t>
+          <t>1263193505</t>
         </is>
       </c>
       <c r="U476" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085320924</t>
+          <t>https://m.place.naver.com/place/1263193505</t>
         </is>
       </c>
       <c r="V476" t="inlineStr">
@@ -44661,25 +44677,29 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>우리이발관</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr"/>
+          <t>개성연출</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>avidasun@naver.com</t>
+        </is>
+      </c>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>031-421-0331</t>
+          <t>031-472-2082</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 흥안대로434번길 51</t>
+          <t>경기도 안양시 만안구 석수로178번길 31 101호</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -44719,13 +44739,13 @@
         </is>
       </c>
       <c r="P477" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q477" t="n">
         <v>0</v>
       </c>
       <c r="R477" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S477" t="inlineStr">
         <is>
@@ -44734,12 +44754,12 @@
       </c>
       <c r="T477" t="inlineStr">
         <is>
-          <t>18679387</t>
+          <t>37147187</t>
         </is>
       </c>
       <c r="U477" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18679387</t>
+          <t>https://m.place.naver.com/place/37147187</t>
         </is>
       </c>
       <c r="V477" t="inlineStr">
@@ -44751,21 +44771,29 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>춘양이발관</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr"/>
+          <t>데아헤어</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>ohnerva@naver.com</t>
+        </is>
+      </c>
       <c r="D478" t="inlineStr"/>
-      <c r="E478" t="inlineStr"/>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>031-444-1320</t>
+        </is>
+      </c>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로510번길 26</t>
+          <t>경기도 안양시 만안구 양화로 137-1</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -44805,30 +44833,4426 @@
         </is>
       </c>
       <c r="P478" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q478" t="n">
         <v>1</v>
       </c>
-      <c r="Q478" t="n">
+      <c r="R478" t="n">
+        <v>33</v>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>619490243</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/619490243</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>레아하우스</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>0507-1347-7356</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관평로 183 2층 204호</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rheahouse_hair_official</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P479" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>58</v>
+      </c>
+      <c r="R479" t="n">
+        <v>464</v>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>1345556524</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1345556524</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>헤어라푼젤 평촌점</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 귀인로190번길 9 1층</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P480" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>2</v>
+      </c>
+      <c r="R480" t="n">
+        <v>113</v>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>1605988314</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1605988314</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>손길헤어</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>cumicoomi@naver.com</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>031-441-1005</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 경수대로 946 대광로제비앙 108호.손길헤어</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P481" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>9</v>
+      </c>
+      <c r="R481" t="n">
+        <v>247</v>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>1064828196</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1064828196</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>깍쟁이</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>waterheat@naver.com</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>031-466-4759</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 삼봉로 15-3</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P482" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>1</v>
+      </c>
+      <c r="R482" t="n">
+        <v>57</v>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>37140413</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37140413</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>헤어앤드 평촌</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>hairand@naver.com</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>031-383-0601</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관평로182번길 51 평촌빌딩 4층 404호</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>https://naver.me/56aGPBlB</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P483" t="n">
+        <v>1834</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>501</v>
+      </c>
+      <c r="R483" t="n">
+        <v>2335</v>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>1974543461</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1974543461</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>궁헤어박달점</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>031-469-5552</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 박달로 517 2층</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P484" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>0</v>
+      </c>
+      <c r="R484" t="n">
+        <v>5</v>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>1094527491</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1094527491</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>엔퍼플헤어</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>npurplehair@naver.com</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>031-471-5239</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 충훈로 81 석수아이파크</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/npurple_salon</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P485" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>33</v>
+      </c>
+      <c r="R485" t="n">
+        <v>86</v>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>34098035</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34098035</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>단발머리</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>031-442-8893</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 박달로 528-1</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P486" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>0</v>
+      </c>
+      <c r="R486" t="n">
+        <v>42</v>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>1014079177</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1014079177</t>
+        </is>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>어바웃헤어</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr"/>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>031-383-3867</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 귀인로190번길 131</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P487" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>1</v>
+      </c>
+      <c r="R487" t="n">
+        <v>68</v>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>37285924</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37285924</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>보보스헤어클럽</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr"/>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>031-473-6509</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 연현로79번길 41 석수 엘지 빌리지</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P488" t="n">
+        <v>214</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>1</v>
+      </c>
+      <c r="R488" t="n">
+        <v>215</v>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>18638741</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18638741</t>
+        </is>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>오유즈 OYUZ</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>dudfo1200@naver.com</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>0507-1399-5240</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 평촌대로 221 센터프라자 3층 302호</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__oyuz</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P489" t="n">
+        <v>1527</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>33</v>
+      </c>
+      <c r="R489" t="n">
+        <v>1560</v>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>1091658228</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1091658228</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>레드헤어살롱 석수점</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>031-474-4141</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 연현로 105 2층</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P490" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="n">
+        <v>49</v>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>31004546</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31004546</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>리아헤어</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>riahair99@naver.com</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>0507-1374-2198</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 임곡로 62 (비산동, 임곡주공프라자) 207호</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P491" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>0</v>
+      </c>
+      <c r="R491" t="n">
+        <v>40</v>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>1254615366</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1254615366</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>투어스헤어</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0507-1461-5860</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관평로 183 평촌자이엘라 109호</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/to_ushair</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P492" t="n">
+        <v>1224</v>
+      </c>
+      <c r="Q492" t="n">
         <v>3</v>
       </c>
-      <c r="R478" t="n">
+      <c r="R492" t="n">
+        <v>1227</v>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>1998775306</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1998775306</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>윤헤어</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>tnwjdgovl84@naver.com</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>031-388-8853</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관평로138번길 53 초원부영상가 1층</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P493" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>0</v>
+      </c>
+      <c r="R493" t="n">
+        <v>84</v>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>1455042272</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455042272</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>토니앤가이 평촌점</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>vanloenpc@naver.com</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>0507-1405-2268</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 시민대로 311 평촌 범계 금강스마트빌딩 202호</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/vanloenpc</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P494" t="n">
+        <v>6318</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>2573</v>
+      </c>
+      <c r="R494" t="n">
+        <v>8891</v>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>20506213</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20506213</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>박승아헤어</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>0507-1441-8039</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 문예로24번길 43 1층 102호</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/psa8711</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P495" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>5</v>
+      </c>
+      <c r="R495" t="n">
+        <v>153</v>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>1250477074</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250477074</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>여운</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>subinok@naver.com</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>0507-1310-2679</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 평촌대로 221 5층 여운</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeoun.h_</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P496" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>5</v>
+      </c>
+      <c r="R496" t="n">
+        <v>199</v>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>1417000372</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1417000372</t>
+        </is>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>헤어하우스</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>birueyeon@naver.com</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>031-442-5877</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 박달로479번길 38</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P497" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>0</v>
+      </c>
+      <c r="R497" t="n">
+        <v>117</v>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>19410440</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19410440</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>클로드헤어</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>0507-1301-9676</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 시민대로 317 대한스마트타워 B동 1층 125호</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_claude_hair</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P498" t="n">
+        <v>1410</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>15</v>
+      </c>
+      <c r="R498" t="n">
+        <v>1425</v>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>1373083210</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1373083210</t>
+        </is>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>블루클럽 안양비산점</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>031-442-0361</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관악대로 133</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P499" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>0</v>
+      </c>
+      <c r="R499" t="n">
+        <v>255</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>1573378596</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1573378596</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>생활,편의</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>키키헤어</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr"/>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>0507-1322-5493</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관악대로 103 3층, 키키헤어 미용실</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr"/>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P500" t="n">
+        <v>1047</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>62</v>
+      </c>
+      <c r="R500" t="n">
+        <v>1109</v>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>1162671504</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1162671504</t>
+        </is>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>보스타바버샵</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>gusdkalsu@naver.com</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>0507-1310-9655</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 동편로39번길 20-13 1층</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>http://instagram.com/bosstha_barbershop</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P501" t="n">
+        <v>1184</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>17</v>
+      </c>
+      <c r="R501" t="n">
+        <v>1201</v>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>1585300866</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1585300866</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>영진이발관</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>kyakult@naver.com</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>031-471-6317</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 석천로171번길 5</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P502" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>0</v>
+      </c>
+      <c r="R502" t="n">
+        <v>19</v>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>1107419428</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1107419428</t>
+        </is>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>하우디바버샵 안양점</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>tlsehd2036@naver.com</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>0507-1440-2807</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 안양로323번길 10 1층 하우디바버샵 안양점</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tlsehd2036</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P503" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>56</v>
+      </c>
+      <c r="R503" t="n">
+        <v>966</v>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>1190201605</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1190201605</t>
+        </is>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>정현이용원</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr"/>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 충훈로93번길 26</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>0</v>
+      </c>
+      <c r="R504" t="n">
+        <v>0</v>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>1850328269</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850328269</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>루앤헤어 안양호계점</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>ttlsunhwa@naver.com</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>0507-1317-3022</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 포도원로 4 2층 루앤헤어 안양호계점</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ttlsunhwa</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr"/>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P505" t="n">
+        <v>2449</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>249</v>
+      </c>
+      <c r="R505" t="n">
+        <v>2698</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>1012904876</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012904876</t>
+        </is>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>선이발관</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>soyen5046@naver.com</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>031-472-5606</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 석수로16번길 56</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr"/>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>1</v>
+      </c>
+      <c r="R506" t="n">
+        <v>1</v>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>37146070</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37146070</t>
+        </is>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>현대이발관</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>sacheoncity@naver.com</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr"/>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 귀인로 195</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>0</v>
+      </c>
+      <c r="R507" t="n">
+        <v>0</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>21136803</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21136803</t>
+        </is>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>현대이발관</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>sacheoncity@naver.com</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 양화로 156</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P508" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>0</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0</v>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>2093976829</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2093976829</t>
+        </is>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>동보이발관</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>chogoya008@naver.com</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>031-471-6971</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 경수대로1201번길 30</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P509" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>0</v>
+      </c>
+      <c r="R509" t="n">
+        <v>1</v>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>37146881</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37146881</t>
+        </is>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>로지바버샵</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>k_s89@naver.com</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr"/>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>0507-1362-3431</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 시민대로159번길 25 134호 로지바버샵</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/k_s89</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P510" t="n">
+        <v>922</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>134</v>
+      </c>
+      <c r="R510" t="n">
+        <v>1056</v>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>1046981391</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046981391</t>
+        </is>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>행운이발관</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>knta_pr@naver.com</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>031-441-5607</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 안양로532번길 41</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>0</v>
+      </c>
+      <c r="R511" t="n">
+        <v>0</v>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>21137869</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21137869</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>리벨로 바버샵</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>rebello1015@naver.com</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>ceo@rebello.co.kr</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>0507-1437-5892</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 시민대로 408 스페이스 블레스 유 2층 리벨로 바버샵</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>https://www.bellobellagroup.com/</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P512" t="n">
+        <v>1597</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>409</v>
+      </c>
+      <c r="R512" t="n">
+        <v>2006</v>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>83867576</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/83867576</t>
+        </is>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>슬리커바버샵</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>0507-1328-1979</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 장내로139번길 56-4 2층 슬리커바버샵</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>http://www.instargram.com/barber__yoonhyuk</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P513" t="n">
+        <v>471</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>18</v>
+      </c>
+      <c r="R513" t="n">
+        <v>489</v>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>1339445993</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1339445993</t>
+        </is>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>뉴금강이발관</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>orseti8300@naver.com</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 양화로135번길 25</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>1</v>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>37145080</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37145080</t>
+        </is>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>레고코르누바버샵 안양</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>sunung418@naver.com</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>0507-1486-0400</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 안양로323번길 40 2층 레고코르누 바버샵</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/regocornubarbershop/</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P515" t="n">
+        <v>844</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>23</v>
+      </c>
+      <c r="R515" t="n">
+        <v>867</v>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>1824492157</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1824492157</t>
+        </is>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>남자는머리빨</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr"/>
+      <c r="D516" t="inlineStr"/>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>0507-1354-0380</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 박달로 501 1층 103호</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P516" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>1</v>
+      </c>
+      <c r="R516" t="n">
+        <v>8</v>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>1667477062</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667477062</t>
+        </is>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>석수이발관</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr"/>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>031-471-8137</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 경수대로1200번길 5</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P517" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>0</v>
+      </c>
+      <c r="R517" t="n">
+        <v>1</v>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>18636113</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18636113</t>
+        </is>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>청주이발소</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>031-383-6995</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관평로138번길 53 초원부영아파트 상가동 2층</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P518" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>0</v>
+      </c>
+      <c r="R518" t="n">
+        <v>5</v>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>1203918736</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203918736</t>
+        </is>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>초원이발관</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>gunsanpr@naver.com</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 양화로105번길 63</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P519" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>0</v>
+      </c>
+      <c r="R519" t="n">
+        <v>1</v>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>21148112</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21148112</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>리웨이바버샵</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>done_barber@naver.com</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 귀인로190번길 70-31 1층</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/done_barber</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P520" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>8</v>
+      </c>
+      <c r="R520" t="n">
+        <v>231</v>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>1739150372</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1739150372</t>
+        </is>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>펜스바버샵 안양본점</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>0507-1345-1423</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 시민대로 230 평촌아크로타워 221호</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fhns_barbershop/</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P521" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>29</v>
+      </c>
+      <c r="R521" t="n">
+        <v>308</v>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>1891047961</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1891047961</t>
+        </is>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>밀리토바버샵</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>style2232@naver.com</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 박달로479번길 23 1층</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/milito_barbershop/</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P522" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q522" t="n">
         <v>4</v>
       </c>
-      <c r="S478" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T478" t="inlineStr">
+      <c r="R522" t="n">
+        <v>229</v>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>1353887934</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1353887934</t>
+        </is>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>준형이발관</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>hayeoneedy0u@naver.com</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 박달로479번길 10</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P523" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>0</v>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>37146400</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37146400</t>
+        </is>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>상상나래헤어샵</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>sangx2narae1@naver.com</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>031-383-1123</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 관악대로 317 2층</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sangx2narae1</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P524" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>9</v>
+      </c>
+      <c r="R524" t="n">
+        <v>25</v>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>2085320924</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2085320924</t>
+        </is>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>우리이발관</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>031-421-0331</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 흥안대로434번길 51</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P525" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>0</v>
+      </c>
+      <c r="R525" t="n">
+        <v>0</v>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>18679387</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18679387</t>
+        </is>
+      </c>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>춘양이발관</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구 안양로510번길 26</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P526" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>3</v>
+      </c>
+      <c r="R526" t="n">
+        <v>4</v>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
         <is>
           <t>19431251</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="U526" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/19431251</t>
         </is>
       </c>
-      <c r="V478" t="inlineStr">
+      <c r="V526" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
